--- a/elenco_scommesse.xlsx
+++ b/elenco_scommesse.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\CLUB12\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\Nuova cartella (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91238B13-FF28-4DF5-A01B-179A71D46D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9D4820-3F93-4818-BFEB-0D40FA836182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="150">
   <si>
     <t>Data e Ora</t>
   </si>
@@ -486,6 +486,9 @@
   </si>
   <si>
     <t>  Santa Clara - Benfica </t>
+  </si>
+  <si>
+    <t> Roma - Cagliari</t>
   </si>
 </sst>
 </file>
@@ -827,7 +830,7 @@
             <c:strRef>
               <c:f>'lista scommesse'!$B:$B</c:f>
               <c:strCache>
-                <c:ptCount val="126"/>
+                <c:ptCount val="127"/>
                 <c:pt idx="0">
                   <c:v>Giorno e Mese</c:v>
                 </c:pt>
@@ -1205,6 +1208,9 @@
                 </c:pt>
                 <c:pt idx="125">
                   <c:v>2026-10-26 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>2026-10-27 0:00:00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1368,7 +1374,7 @@
             <c:strRef>
               <c:f>'lista scommesse'!$B:$B</c:f>
               <c:strCache>
-                <c:ptCount val="126"/>
+                <c:ptCount val="127"/>
                 <c:pt idx="0">
                   <c:v>Giorno e Mese</c:v>
                 </c:pt>
@@ -1746,6 +1752,9 @@
                 </c:pt>
                 <c:pt idx="125">
                   <c:v>2026-10-26 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>2026-10-27 0:00:00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2366,7 +2375,7 @@
       </c>
       <c r="S2" s="3">
         <f>COUNTA(L:L)-1</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -2502,7 +2511,7 @@
       </c>
       <c r="S4" s="5">
         <f>SUM(M:M)</f>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -2570,7 +2579,7 @@
       </c>
       <c r="S5" s="7">
         <f>S4/S3</f>
-        <v>-0.25659999999999988</v>
+        <v>-0.29659999999999992</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -9134,7 +9143,7 @@
         <v>46320</v>
       </c>
       <c r="B113" s="13">
-        <f t="shared" ref="B113:B131" si="33">A113</f>
+        <f t="shared" ref="B113:B120" si="33">A113</f>
         <v>46320</v>
       </c>
       <c r="C113" s="13" t="s">
@@ -9622,7 +9631,7 @@
         <v>46321</v>
       </c>
       <c r="B121" s="13">
-        <f t="shared" ref="B121:B131" si="39">A121</f>
+        <f t="shared" ref="B121:B127" si="39">A121</f>
         <v>46321</v>
       </c>
       <c r="C121" s="13" t="s">
@@ -9984,38 +9993,59 @@
       <c r="Z126" s="3"/>
     </row>
     <row r="127" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A127" s="13"/>
-      <c r="B127" s="13"/>
-      <c r="C127" s="13"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="14"/>
-      <c r="F127" s="14"/>
-      <c r="G127" s="15"/>
-      <c r="H127" s="18" t="e">
+      <c r="A127" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B127" s="13">
+        <f t="shared" si="39"/>
+        <v>46322</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G127" s="15">
+        <v>5</v>
+      </c>
+      <c r="H127" s="18">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I127" s="14"/>
-      <c r="J127" s="14"/>
+        <v>6.8914334181509673</v>
+      </c>
+      <c r="I127" s="14">
+        <v>1.44</v>
+      </c>
+      <c r="J127" s="14">
+        <v>1.31</v>
+      </c>
       <c r="K127" s="16">
         <v>5</v>
       </c>
-      <c r="L127" s="14"/>
+      <c r="L127" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="M127" s="17">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N127" s="17" t="e">
+        <v>-5</v>
+      </c>
+      <c r="N127" s="17">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v>0.34457167090754837</v>
       </c>
       <c r="O127" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
-      </c>
-      <c r="P127" s="17" t="e">
+        <v>-37.074999999999989</v>
+      </c>
+      <c r="P127" s="17">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v>57.831041522017372</v>
       </c>
       <c r="V127" s="3"/>
       <c r="W127" s="3"/>
@@ -10051,7 +10081,7 @@
       </c>
       <c r="O128" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P128" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10091,7 +10121,7 @@
       </c>
       <c r="O129" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P129" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10131,7 +10161,7 @@
       </c>
       <c r="O130" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P130" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10171,7 +10201,7 @@
       </c>
       <c r="O131" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P131" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10211,7 +10241,7 @@
       </c>
       <c r="O132" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P132" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10251,7 +10281,7 @@
       </c>
       <c r="O133" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P133" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10291,7 +10321,7 @@
       </c>
       <c r="O134" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P134" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10331,7 +10361,7 @@
       </c>
       <c r="O135" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P135" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10371,7 +10401,7 @@
       </c>
       <c r="O136" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P136" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10411,7 +10441,7 @@
       </c>
       <c r="O137" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P137" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10451,7 +10481,7 @@
       </c>
       <c r="O138" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P138" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10491,7 +10521,7 @@
       </c>
       <c r="O139" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P139" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10531,7 +10561,7 @@
       </c>
       <c r="O140" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P140" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10571,7 +10601,7 @@
       </c>
       <c r="O141" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P141" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10611,7 +10641,7 @@
       </c>
       <c r="O142" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P142" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10651,7 +10681,7 @@
       </c>
       <c r="O143" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P143" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10691,7 +10721,7 @@
       </c>
       <c r="O144" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P144" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10731,7 +10761,7 @@
       </c>
       <c r="O145" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P145" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10771,7 +10801,7 @@
       </c>
       <c r="O146" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P146" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10811,7 +10841,7 @@
       </c>
       <c r="O147" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P147" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10851,7 +10881,7 @@
       </c>
       <c r="O148" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P148" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10891,7 +10921,7 @@
       </c>
       <c r="O149" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P149" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10931,7 +10961,7 @@
       </c>
       <c r="O150" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P150" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10971,7 +11001,7 @@
       </c>
       <c r="O151" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P151" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11011,7 +11041,7 @@
       </c>
       <c r="O152" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P152" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11051,7 +11081,7 @@
       </c>
       <c r="O153" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P153" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11091,7 +11121,7 @@
       </c>
       <c r="O154" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P154" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11131,7 +11161,7 @@
       </c>
       <c r="O155" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P155" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11171,7 +11201,7 @@
       </c>
       <c r="O156" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P156" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11211,7 +11241,7 @@
       </c>
       <c r="O157" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P157" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11251,7 +11281,7 @@
       </c>
       <c r="O158" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P158" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11291,7 +11321,7 @@
       </c>
       <c r="O159" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P159" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11331,7 +11361,7 @@
       </c>
       <c r="O160" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P160" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11371,7 +11401,7 @@
       </c>
       <c r="O161" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P161" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11411,7 +11441,7 @@
       </c>
       <c r="O162" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P162" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11451,7 +11481,7 @@
       </c>
       <c r="O163" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P163" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11491,7 +11521,7 @@
       </c>
       <c r="O164" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P164" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11531,7 +11561,7 @@
       </c>
       <c r="O165" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P165" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11571,7 +11601,7 @@
       </c>
       <c r="O166" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P166" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11611,7 +11641,7 @@
       </c>
       <c r="O167" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P167" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11651,7 +11681,7 @@
       </c>
       <c r="O168" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P168" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11691,7 +11721,7 @@
       </c>
       <c r="O169" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P169" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11731,7 +11761,7 @@
       </c>
       <c r="O170" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P170" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11771,7 +11801,7 @@
       </c>
       <c r="O171" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P171" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11811,7 +11841,7 @@
       </c>
       <c r="O172" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P172" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11851,7 +11881,7 @@
       </c>
       <c r="O173" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P173" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11891,7 +11921,7 @@
       </c>
       <c r="O174" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P174" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11931,7 +11961,7 @@
       </c>
       <c r="O175" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P175" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11971,7 +12001,7 @@
       </c>
       <c r="O176" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P176" s="17" t="e">
         <f t="shared" si="38"/>
@@ -12011,7 +12041,7 @@
       </c>
       <c r="O177" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P177" s="17" t="e">
         <f t="shared" si="38"/>
@@ -12051,7 +12081,7 @@
       </c>
       <c r="O178" s="17">
         <f t="shared" si="37"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P178" s="17" t="e">
         <f t="shared" si="38"/>
@@ -12091,7 +12121,7 @@
       </c>
       <c r="O179" s="17">
         <f t="shared" ref="O179:O226" si="43">M179+O178</f>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P179" s="17" t="e">
         <f t="shared" ref="P179:P226" si="44">P178+N179</f>
@@ -12131,7 +12161,7 @@
       </c>
       <c r="O180" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P180" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12171,7 +12201,7 @@
       </c>
       <c r="O181" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P181" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12211,7 +12241,7 @@
       </c>
       <c r="O182" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P182" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12251,7 +12281,7 @@
       </c>
       <c r="O183" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P183" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12291,7 +12321,7 @@
       </c>
       <c r="O184" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P184" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12331,7 +12361,7 @@
       </c>
       <c r="O185" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P185" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12371,7 +12401,7 @@
       </c>
       <c r="O186" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P186" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12411,7 +12441,7 @@
       </c>
       <c r="O187" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P187" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12451,7 +12481,7 @@
       </c>
       <c r="O188" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P188" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12491,7 +12521,7 @@
       </c>
       <c r="O189" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P189" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12531,7 +12561,7 @@
       </c>
       <c r="O190" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P190" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12571,7 +12601,7 @@
       </c>
       <c r="O191" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P191" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12611,7 +12641,7 @@
       </c>
       <c r="O192" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P192" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12651,7 +12681,7 @@
       </c>
       <c r="O193" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P193" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12691,7 +12721,7 @@
       </c>
       <c r="O194" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P194" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12731,7 +12761,7 @@
       </c>
       <c r="O195" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P195" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12771,7 +12801,7 @@
       </c>
       <c r="O196" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P196" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12811,7 +12841,7 @@
       </c>
       <c r="O197" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P197" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12851,7 +12881,7 @@
       </c>
       <c r="O198" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P198" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12891,7 +12921,7 @@
       </c>
       <c r="O199" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P199" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12931,7 +12961,7 @@
       </c>
       <c r="O200" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P200" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12971,7 +13001,7 @@
       </c>
       <c r="O201" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P201" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13011,7 +13041,7 @@
       </c>
       <c r="O202" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P202" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13051,7 +13081,7 @@
       </c>
       <c r="O203" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P203" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13091,7 +13121,7 @@
       </c>
       <c r="O204" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P204" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13131,7 +13161,7 @@
       </c>
       <c r="O205" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P205" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13171,7 +13201,7 @@
       </c>
       <c r="O206" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P206" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13211,7 +13241,7 @@
       </c>
       <c r="O207" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P207" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13251,7 +13281,7 @@
       </c>
       <c r="O208" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P208" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13291,7 +13321,7 @@
       </c>
       <c r="O209" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P209" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13331,7 +13361,7 @@
       </c>
       <c r="O210" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P210" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13371,7 +13401,7 @@
       </c>
       <c r="O211" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P211" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13411,7 +13441,7 @@
       </c>
       <c r="O212" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P212" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13451,7 +13481,7 @@
       </c>
       <c r="O213" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P213" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13491,7 +13521,7 @@
       </c>
       <c r="O214" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P214" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13531,7 +13561,7 @@
       </c>
       <c r="O215" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P215" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13571,7 +13601,7 @@
       </c>
       <c r="O216" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P216" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13611,7 +13641,7 @@
       </c>
       <c r="O217" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P217" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13651,7 +13681,7 @@
       </c>
       <c r="O218" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P218" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13691,7 +13721,7 @@
       </c>
       <c r="O219" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P219" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13731,7 +13761,7 @@
       </c>
       <c r="O220" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P220" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13771,7 +13801,7 @@
       </c>
       <c r="O221" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P221" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13811,7 +13841,7 @@
       </c>
       <c r="O222" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P222" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13851,7 +13881,7 @@
       </c>
       <c r="O223" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P223" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13889,7 +13919,7 @@
       </c>
       <c r="O224" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P224" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13927,7 +13957,7 @@
       </c>
       <c r="O225" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P225" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13965,7 +13995,7 @@
       </c>
       <c r="O226" s="17">
         <f t="shared" si="43"/>
-        <v>-32.074999999999989</v>
+        <v>-37.074999999999989</v>
       </c>
       <c r="P226" s="17" t="e">
         <f t="shared" si="44"/>

--- a/elenco_scommesse.xlsx
+++ b/elenco_scommesse.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\Nuova cartella (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9D4820-3F93-4818-BFEB-0D40FA836182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7E88D4-60EC-4393-A4F3-4822413A466D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="154">
   <si>
     <t>Data e Ora</t>
   </si>
@@ -489,6 +489,18 @@
   </si>
   <si>
     <t> Roma - Cagliari</t>
+  </si>
+  <si>
+    <t> Genoa - Juventus </t>
+  </si>
+  <si>
+    <t>Milan - Bologna</t>
+  </si>
+  <si>
+    <t>POKERSTARS</t>
+  </si>
+  <si>
+    <t> Monza - Napoli </t>
   </si>
 </sst>
 </file>
@@ -830,7 +842,7 @@
             <c:strRef>
               <c:f>'lista scommesse'!$B:$B</c:f>
               <c:strCache>
-                <c:ptCount val="127"/>
+                <c:ptCount val="133"/>
                 <c:pt idx="0">
                   <c:v>Giorno e Mese</c:v>
                 </c:pt>
@@ -1211,6 +1223,24 @@
                 </c:pt>
                 <c:pt idx="126">
                   <c:v>2026-10-27 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2026-10-28 0:00:00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1374,7 +1404,7 @@
             <c:strRef>
               <c:f>'lista scommesse'!$B:$B</c:f>
               <c:strCache>
-                <c:ptCount val="127"/>
+                <c:ptCount val="133"/>
                 <c:pt idx="0">
                   <c:v>Giorno e Mese</c:v>
                 </c:pt>
@@ -1755,6 +1785,24 @@
                 </c:pt>
                 <c:pt idx="126">
                   <c:v>2026-10-27 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>2026-10-28 0:00:00</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2026-10-28 0:00:00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2375,7 +2423,7 @@
       </c>
       <c r="S2" s="3">
         <f>COUNTA(L:L)-1</f>
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -2511,7 +2559,7 @@
       </c>
       <c r="S4" s="5">
         <f>SUM(M:M)</f>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -2579,7 +2627,7 @@
       </c>
       <c r="S5" s="7">
         <f>S4/S3</f>
-        <v>-0.29659999999999992</v>
+        <v>-0.25739999999999985</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -9631,7 +9679,7 @@
         <v>46321</v>
       </c>
       <c r="B121" s="13">
-        <f t="shared" ref="B121:B127" si="39">A121</f>
+        <f t="shared" ref="B121:B133" si="39">A121</f>
         <v>46321</v>
       </c>
       <c r="C121" s="13" t="s">
@@ -10054,38 +10102,59 @@
       <c r="Z127" s="3"/>
     </row>
     <row r="128" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A128" s="13"/>
-      <c r="B128" s="13"/>
-      <c r="C128" s="13"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="14"/>
-      <c r="F128" s="14"/>
-      <c r="G128" s="15"/>
-      <c r="H128" s="18" t="e">
+      <c r="A128" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B128" s="13">
+        <f t="shared" si="39"/>
+        <v>46323</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E128" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G128" s="15">
+        <v>5</v>
+      </c>
+      <c r="H128" s="18">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I128" s="14"/>
-      <c r="J128" s="14"/>
+        <v>5.3571428571428541</v>
+      </c>
+      <c r="I128" s="14">
+        <v>1.75</v>
+      </c>
+      <c r="J128" s="14">
+        <v>1.6</v>
+      </c>
       <c r="K128" s="16">
         <v>5</v>
       </c>
-      <c r="L128" s="14"/>
+      <c r="L128" s="14" t="s">
+        <v>22</v>
+      </c>
       <c r="M128" s="17">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N128" s="17" t="e">
+        <v>3.75</v>
+      </c>
+      <c r="N128" s="17">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v>0.26785714285714268</v>
       </c>
       <c r="O128" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
-      </c>
-      <c r="P128" s="17" t="e">
+        <v>-33.324999999999989</v>
+      </c>
+      <c r="P128" s="17">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v>58.098898664874518</v>
       </c>
       <c r="V128" s="3"/>
       <c r="W128" s="3"/>
@@ -10094,38 +10163,59 @@
       <c r="Z128" s="3"/>
     </row>
     <row r="129" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A129" s="13"/>
-      <c r="B129" s="13"/>
-      <c r="C129" s="13"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="14"/>
-      <c r="F129" s="14"/>
-      <c r="G129" s="15"/>
-      <c r="H129" s="18" t="e">
+      <c r="A129" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B129" s="13">
+        <f t="shared" si="39"/>
+        <v>46323</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D129" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G129" s="15">
+        <v>5</v>
+      </c>
+      <c r="H129" s="18">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I129" s="14"/>
-      <c r="J129" s="14"/>
+        <v>6.6948192398805162</v>
+      </c>
+      <c r="I129" s="14">
+        <v>1.46</v>
+      </c>
+      <c r="J129" s="14">
+        <v>1.33</v>
+      </c>
       <c r="K129" s="16">
         <v>5</v>
       </c>
-      <c r="L129" s="14"/>
+      <c r="L129" s="14" t="s">
+        <v>22</v>
+      </c>
       <c r="M129" s="17">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N129" s="17" t="e">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="N129" s="17">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v>0.33474096199402581</v>
       </c>
       <c r="O129" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
-      </c>
-      <c r="P129" s="17" t="e">
+        <v>-31.024999999999988</v>
+      </c>
+      <c r="P129" s="17">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v>58.433639626868541</v>
       </c>
       <c r="V129" s="3"/>
       <c r="W129" s="3"/>
@@ -10134,38 +10224,59 @@
       <c r="Z129" s="3"/>
     </row>
     <row r="130" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A130" s="13"/>
-      <c r="B130" s="13"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="14"/>
-      <c r="F130" s="14"/>
-      <c r="G130" s="15"/>
-      <c r="H130" s="18" t="e">
+      <c r="A130" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B130" s="13">
+        <f t="shared" si="39"/>
+        <v>46323</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E130" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G130" s="15">
+        <v>5</v>
+      </c>
+      <c r="H130" s="18">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I130" s="14"/>
-      <c r="J130" s="14"/>
+        <v>8.7492125708686217</v>
+      </c>
+      <c r="I130" s="14">
+        <v>1.82</v>
+      </c>
+      <c r="J130" s="14">
+        <v>1.57</v>
+      </c>
       <c r="K130" s="16">
         <v>5</v>
       </c>
-      <c r="L130" s="14"/>
+      <c r="L130" s="14" t="s">
+        <v>22</v>
+      </c>
       <c r="M130" s="17">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N130" s="17" t="e">
+        <v>4.1000000000000005</v>
+      </c>
+      <c r="N130" s="17">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v>0.43746062854343104</v>
       </c>
       <c r="O130" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
-      </c>
-      <c r="P130" s="17" t="e">
+        <v>-26.924999999999986</v>
+      </c>
+      <c r="P130" s="17">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v>58.871100255411974</v>
       </c>
       <c r="V130" s="3"/>
       <c r="W130" s="3"/>
@@ -10174,38 +10285,59 @@
       <c r="Z130" s="3"/>
     </row>
     <row r="131" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A131" s="13"/>
-      <c r="B131" s="13"/>
-      <c r="C131" s="13"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="14"/>
-      <c r="F131" s="14"/>
-      <c r="G131" s="15"/>
-      <c r="H131" s="18" t="e">
+      <c r="A131" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B131" s="13">
+        <f t="shared" si="39"/>
+        <v>46323</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D131" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F131" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G131" s="15">
+        <v>5</v>
+      </c>
+      <c r="H131" s="18">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I131" s="14"/>
-      <c r="J131" s="14"/>
+        <v>7.4226333219138922</v>
+      </c>
+      <c r="I131" s="14">
+        <v>1.39</v>
+      </c>
+      <c r="J131" s="14">
+        <v>1.26</v>
+      </c>
       <c r="K131" s="16">
         <v>5</v>
       </c>
-      <c r="L131" s="14"/>
+      <c r="L131" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="M131" s="17">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N131" s="17" t="e">
+        <v>-5</v>
+      </c>
+      <c r="N131" s="17">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v>0.37113166609569459</v>
       </c>
       <c r="O131" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
-      </c>
-      <c r="P131" s="17" t="e">
+        <v>-31.924999999999986</v>
+      </c>
+      <c r="P131" s="17">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v>59.242231921507667</v>
       </c>
       <c r="V131" s="3"/>
       <c r="W131" s="3"/>
@@ -10214,38 +10346,59 @@
       <c r="Z131" s="3"/>
     </row>
     <row r="132" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A132" s="13"/>
-      <c r="B132" s="13"/>
-      <c r="C132" s="13"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="14"/>
-      <c r="F132" s="14"/>
-      <c r="G132" s="15"/>
-      <c r="H132" s="18" t="e">
+      <c r="A132" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B132" s="13">
+        <f t="shared" si="39"/>
+        <v>46323</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E132" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G132" s="15">
+        <v>5</v>
+      </c>
+      <c r="H132" s="18">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I132" s="14"/>
-      <c r="J132" s="14"/>
+        <v>9.2663599182004077</v>
+      </c>
+      <c r="I132" s="14">
+        <v>1.92</v>
+      </c>
+      <c r="J132" s="14">
+        <v>1.63</v>
+      </c>
       <c r="K132" s="16">
         <v>5</v>
       </c>
-      <c r="L132" s="14"/>
+      <c r="L132" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="M132" s="17">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N132" s="17" t="e">
+        <v>-5</v>
+      </c>
+      <c r="N132" s="17">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v>0.46331799591002037</v>
       </c>
       <c r="O132" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
-      </c>
-      <c r="P132" s="17" t="e">
+        <v>-36.924999999999983</v>
+      </c>
+      <c r="P132" s="17">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v>59.705549917417684</v>
       </c>
       <c r="V132" s="3"/>
       <c r="W132" s="3"/>
@@ -10254,38 +10407,59 @@
       <c r="Z132" s="3"/>
     </row>
     <row r="133" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A133" s="13"/>
-      <c r="B133" s="13"/>
-      <c r="C133" s="13"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="14"/>
-      <c r="F133" s="14"/>
-      <c r="G133" s="15"/>
-      <c r="H133" s="18" t="e">
+      <c r="A133" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B133" s="13">
+        <f t="shared" si="39"/>
+        <v>46323</v>
+      </c>
+      <c r="C133" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D133" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="F133" s="14">
+        <v>2</v>
+      </c>
+      <c r="G133" s="15">
+        <v>5</v>
+      </c>
+      <c r="H133" s="18">
         <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I133" s="14"/>
-      <c r="J133" s="14"/>
+        <v>12.412216233872279</v>
+      </c>
+      <c r="I133" s="14">
+        <v>1.95</v>
+      </c>
+      <c r="J133" s="14">
+        <v>1.57</v>
+      </c>
       <c r="K133" s="16">
         <v>5</v>
       </c>
-      <c r="L133" s="14"/>
+      <c r="L133" s="14" t="s">
+        <v>22</v>
+      </c>
       <c r="M133" s="17">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="N133" s="17" t="e">
+        <v>4.75</v>
+      </c>
+      <c r="N133" s="17">
         <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
+        <v>0.62061081169361398</v>
       </c>
       <c r="O133" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
-      </c>
-      <c r="P133" s="17" t="e">
+        <v>-32.174999999999983</v>
+      </c>
+      <c r="P133" s="17">
         <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
+        <v>60.326160729111301</v>
       </c>
       <c r="V133" s="3"/>
       <c r="W133" s="3"/>
@@ -10321,7 +10495,7 @@
       </c>
       <c r="O134" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P134" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10361,7 +10535,7 @@
       </c>
       <c r="O135" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P135" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10401,7 +10575,7 @@
       </c>
       <c r="O136" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P136" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10441,7 +10615,7 @@
       </c>
       <c r="O137" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P137" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10481,7 +10655,7 @@
       </c>
       <c r="O138" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P138" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10521,7 +10695,7 @@
       </c>
       <c r="O139" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P139" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10561,7 +10735,7 @@
       </c>
       <c r="O140" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P140" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10601,7 +10775,7 @@
       </c>
       <c r="O141" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P141" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10641,7 +10815,7 @@
       </c>
       <c r="O142" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P142" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10681,7 +10855,7 @@
       </c>
       <c r="O143" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P143" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10721,7 +10895,7 @@
       </c>
       <c r="O144" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P144" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10761,7 +10935,7 @@
       </c>
       <c r="O145" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P145" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10801,7 +10975,7 @@
       </c>
       <c r="O146" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P146" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10841,7 +11015,7 @@
       </c>
       <c r="O147" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P147" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10881,7 +11055,7 @@
       </c>
       <c r="O148" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P148" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10921,7 +11095,7 @@
       </c>
       <c r="O149" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P149" s="17" t="e">
         <f t="shared" si="38"/>
@@ -10961,7 +11135,7 @@
       </c>
       <c r="O150" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P150" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11001,7 +11175,7 @@
       </c>
       <c r="O151" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P151" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11041,7 +11215,7 @@
       </c>
       <c r="O152" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P152" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11081,7 +11255,7 @@
       </c>
       <c r="O153" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P153" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11121,7 +11295,7 @@
       </c>
       <c r="O154" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P154" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11161,7 +11335,7 @@
       </c>
       <c r="O155" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P155" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11201,7 +11375,7 @@
       </c>
       <c r="O156" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P156" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11241,7 +11415,7 @@
       </c>
       <c r="O157" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P157" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11281,7 +11455,7 @@
       </c>
       <c r="O158" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P158" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11321,7 +11495,7 @@
       </c>
       <c r="O159" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P159" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11361,7 +11535,7 @@
       </c>
       <c r="O160" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P160" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11401,7 +11575,7 @@
       </c>
       <c r="O161" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P161" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11441,7 +11615,7 @@
       </c>
       <c r="O162" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P162" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11481,7 +11655,7 @@
       </c>
       <c r="O163" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P163" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11521,7 +11695,7 @@
       </c>
       <c r="O164" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P164" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11561,7 +11735,7 @@
       </c>
       <c r="O165" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P165" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11601,7 +11775,7 @@
       </c>
       <c r="O166" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P166" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11641,7 +11815,7 @@
       </c>
       <c r="O167" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P167" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11681,7 +11855,7 @@
       </c>
       <c r="O168" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P168" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11721,7 +11895,7 @@
       </c>
       <c r="O169" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P169" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11761,7 +11935,7 @@
       </c>
       <c r="O170" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P170" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11801,7 +11975,7 @@
       </c>
       <c r="O171" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P171" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11841,7 +12015,7 @@
       </c>
       <c r="O172" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P172" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11881,7 +12055,7 @@
       </c>
       <c r="O173" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P173" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11921,7 +12095,7 @@
       </c>
       <c r="O174" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P174" s="17" t="e">
         <f t="shared" si="38"/>
@@ -11961,7 +12135,7 @@
       </c>
       <c r="O175" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P175" s="17" t="e">
         <f t="shared" si="38"/>
@@ -12001,7 +12175,7 @@
       </c>
       <c r="O176" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P176" s="17" t="e">
         <f t="shared" si="38"/>
@@ -12041,7 +12215,7 @@
       </c>
       <c r="O177" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P177" s="17" t="e">
         <f t="shared" si="38"/>
@@ -12081,7 +12255,7 @@
       </c>
       <c r="O178" s="17">
         <f t="shared" si="37"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P178" s="17" t="e">
         <f t="shared" si="38"/>
@@ -12121,7 +12295,7 @@
       </c>
       <c r="O179" s="17">
         <f t="shared" ref="O179:O226" si="43">M179+O178</f>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P179" s="17" t="e">
         <f t="shared" ref="P179:P226" si="44">P178+N179</f>
@@ -12161,7 +12335,7 @@
       </c>
       <c r="O180" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P180" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12201,7 +12375,7 @@
       </c>
       <c r="O181" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P181" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12241,7 +12415,7 @@
       </c>
       <c r="O182" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P182" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12281,7 +12455,7 @@
       </c>
       <c r="O183" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P183" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12321,7 +12495,7 @@
       </c>
       <c r="O184" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P184" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12361,7 +12535,7 @@
       </c>
       <c r="O185" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P185" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12401,7 +12575,7 @@
       </c>
       <c r="O186" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P186" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12441,7 +12615,7 @@
       </c>
       <c r="O187" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P187" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12481,7 +12655,7 @@
       </c>
       <c r="O188" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P188" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12521,7 +12695,7 @@
       </c>
       <c r="O189" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P189" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12561,7 +12735,7 @@
       </c>
       <c r="O190" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P190" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12601,7 +12775,7 @@
       </c>
       <c r="O191" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P191" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12641,7 +12815,7 @@
       </c>
       <c r="O192" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P192" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12681,7 +12855,7 @@
       </c>
       <c r="O193" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P193" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12721,7 +12895,7 @@
       </c>
       <c r="O194" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P194" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12761,7 +12935,7 @@
       </c>
       <c r="O195" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P195" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12801,7 +12975,7 @@
       </c>
       <c r="O196" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P196" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12841,7 +13015,7 @@
       </c>
       <c r="O197" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P197" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12881,7 +13055,7 @@
       </c>
       <c r="O198" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P198" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12921,7 +13095,7 @@
       </c>
       <c r="O199" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P199" s="17" t="e">
         <f t="shared" si="44"/>
@@ -12961,7 +13135,7 @@
       </c>
       <c r="O200" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P200" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13001,7 +13175,7 @@
       </c>
       <c r="O201" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P201" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13041,7 +13215,7 @@
       </c>
       <c r="O202" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P202" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13081,7 +13255,7 @@
       </c>
       <c r="O203" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P203" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13121,7 +13295,7 @@
       </c>
       <c r="O204" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P204" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13161,7 +13335,7 @@
       </c>
       <c r="O205" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P205" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13201,7 +13375,7 @@
       </c>
       <c r="O206" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P206" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13241,7 +13415,7 @@
       </c>
       <c r="O207" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P207" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13281,7 +13455,7 @@
       </c>
       <c r="O208" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P208" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13321,7 +13495,7 @@
       </c>
       <c r="O209" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P209" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13361,7 +13535,7 @@
       </c>
       <c r="O210" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P210" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13401,7 +13575,7 @@
       </c>
       <c r="O211" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P211" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13441,7 +13615,7 @@
       </c>
       <c r="O212" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P212" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13481,7 +13655,7 @@
       </c>
       <c r="O213" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P213" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13521,7 +13695,7 @@
       </c>
       <c r="O214" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P214" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13561,7 +13735,7 @@
       </c>
       <c r="O215" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P215" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13601,7 +13775,7 @@
       </c>
       <c r="O216" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P216" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13641,7 +13815,7 @@
       </c>
       <c r="O217" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P217" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13681,7 +13855,7 @@
       </c>
       <c r="O218" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P218" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13721,7 +13895,7 @@
       </c>
       <c r="O219" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P219" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13761,7 +13935,7 @@
       </c>
       <c r="O220" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P220" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13801,7 +13975,7 @@
       </c>
       <c r="O221" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P221" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13841,7 +14015,7 @@
       </c>
       <c r="O222" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P222" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13881,7 +14055,7 @@
       </c>
       <c r="O223" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P223" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13919,7 +14093,7 @@
       </c>
       <c r="O224" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P224" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13957,7 +14131,7 @@
       </c>
       <c r="O225" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P225" s="17" t="e">
         <f t="shared" si="44"/>
@@ -13995,7 +14169,7 @@
       </c>
       <c r="O226" s="17">
         <f t="shared" si="43"/>
-        <v>-37.074999999999989</v>
+        <v>-32.174999999999983</v>
       </c>
       <c r="P226" s="17" t="e">
         <f t="shared" si="44"/>
